--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487507_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487507_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1014</v>
+        <v>4.0213</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3519</v>
+        <v>-1.5831</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7495</v>
+        <v>5.6044</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9523</v>
+        <v>1.0439</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0013</v>
+        <v>0.9983</v>
       </c>
       <c r="I2" t="n">
-        <v>1.951</v>
+        <v>0.0456</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1764</v>
+        <v>-1.1632</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4102</v>
+        <v>0.3129</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5866</v>
+        <v>-1.4761</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2241</v>
+        <v>2.207</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4114</v>
+        <v>0.6854</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6355</v>
+        <v>1.5217</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7834</v>
+        <v>2.3502</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7626</v>
+        <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3657</v>
+        <v>0.9026</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1206</v>
+        <v>-0.4199</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4863</v>
+        <v>1.3226</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>-0.2754</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6117</v>
+        <v>3.4453</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.966</v>
+        <v>1.2661</v>
       </c>
       <c r="F3" t="n">
-        <v>5.5777</v>
+        <v>2.1792</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0439</v>
+        <v>1.9523</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9983</v>
+        <v>0.0013</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0456</v>
+        <v>1.951</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.1632</v>
+        <v>2.1764</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3129</v>
+        <v>-0.4102</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.4761</v>
+        <v>2.5866</v>
       </c>
       <c r="M3" t="n">
-        <v>2.207</v>
+        <v>-0.2241</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6854</v>
+        <v>0.4114</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5217</v>
+        <v>-0.6355</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3502</v>
+        <v>0.7834</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3502</v>
+        <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>0.493</v>
+        <v>0.7096</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8028</v>
+        <v>-0.2064</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2958</v>
+        <v>0.916</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X3" t="n">
         <v>-0.2754</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6448</v>
+        <v>0.6073</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1837</v>
+        <v>-2.4351</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8285</v>
+        <v>3.0424</v>
       </c>
       <c r="G4" t="n">
         <v>2.4582</v>
@@ -766,13 +766,13 @@
         <v>2.1543</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2038</v>
+        <v>1.1663</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9648</v>
+        <v>0.7134</v>
       </c>
       <c r="U4" t="n">
-        <v>0.239</v>
+        <v>0.4529</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2754</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5295</v>
+        <v>0.499</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0363</v>
+        <v>0.0508</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5657</v>
+        <v>0.4482</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.064</v>
+        <v>0.556</v>
       </c>
       <c r="H5" t="n">
-        <v>0.375</v>
+        <v>-0.3331</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.439</v>
+        <v>0.8891</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1131</v>
+        <v>0.6019</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0323</v>
+        <v>-0.5393</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0808</v>
+        <v>1.1413</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1772</v>
+        <v>-0.0459</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3427</v>
+        <v>0.2062</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5198</v>
+        <v>-0.2521</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1899</v>
+        <v>-0.9567</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1494</v>
+        <v>-0.5511</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0405</v>
+        <v>-0.4057</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2571</v>
+        <v>0.3205</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1109</v>
+        <v>-0.1651</v>
       </c>
       <c r="F6" t="n">
-        <v>0.368</v>
+        <v>0.4855</v>
       </c>
       <c r="G6" t="n">
-        <v>0.556</v>
+        <v>-0.064</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3331</v>
+        <v>0.375</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8891</v>
+        <v>-0.439</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6019</v>
+        <v>0.1131</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5393</v>
+        <v>0.0323</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1413</v>
+        <v>0.0808</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0459</v>
+        <v>-0.1772</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2062</v>
+        <v>0.3427</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2521</v>
+        <v>-0.5198</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1987</v>
+        <v>-0.3989</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7128</v>
+        <v>-0.2782</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4859</v>
+        <v>-0.1207</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.766</v>
+        <v>-1.116</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1545</v>
+        <v>-1.7451</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3885</v>
+        <v>0.6291</v>
       </c>
       <c r="G7" t="n">
         <v>1.7175</v>
@@ -1000,13 +1000,13 @@
         <v>1.9585</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2876</v>
+        <v>-0.6377</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7722</v>
+        <v>-0.3629</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5154</v>
+        <v>-0.2748</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2166</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1584</v>
+        <v>-2.6427</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.4598</v>
+        <v>-4.4629</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3014</v>
+        <v>1.8202</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9821</v>
@@ -1078,13 +1078,13 @@
         <v>2.546</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8054</v>
+        <v>-0.2897</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.7821</v>
+        <v>-0.7852</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9767</v>
+        <v>0.4955</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3065</v>
+        <v>-3.0751</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6401</v>
+        <v>-1.4354</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6665</v>
+        <v>-1.6398</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8764</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4509</v>
+        <v>-0.2195</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0594</v>
+        <v>0.1453</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3915</v>
+        <v>-0.3648</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.0067</v>
+        <v>-8.9739</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.1769</v>
+        <v>-8.3847</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8298</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3326</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9346</v>
+        <v>-0.9018</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3068</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6277</v>
+        <v>-0.3871</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9977</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.093100000000002</v>
+        <v>-6.914300000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-19.3763</v>
+        <v>-18.8945</v>
       </c>
       <c r="F11" t="n">
-        <v>12.283</v>
+        <v>11.98</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4728</v>
+        <v>1.472800000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7474</v>
+        <v>3.747399999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2743</v>
+        <v>-2.274299999999999</v>
       </c>
       <c r="J11" t="n">
         <v>1.0041</v>
@@ -1294,16 +1294,16 @@
         <v>2.5991</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4685999999999997</v>
+        <v>0.4686000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>5.3423</v>
+        <v>5.342300000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-4.8735</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.721</v>
+        <v>-3.720999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-17.6263</v>
@@ -1312,13 +1312,13 @@
         <v>13.9052</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8045999999999998</v>
+        <v>-0.6257999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.7413</v>
+        <v>-2.2596</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9368</v>
+        <v>1.6339</v>
       </c>
       <c r="V11" t="n">
         <v>-4.0405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.8474</v>
+        <v>7.4791</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1827</v>
+        <v>3.75</v>
       </c>
       <c r="F12" t="n">
-        <v>4.6647</v>
+        <v>3.7291</v>
       </c>
       <c r="G12" t="n">
         <v>3.7446</v>
@@ -1390,13 +1390,13 @@
         <v>2.7419</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3978</v>
+        <v>2.0295</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9614</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4364</v>
+        <v>1.5008</v>
       </c>
       <c r="V12" t="n">
         <v>-0.0576</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4212</v>
+        <v>3.8352</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6584</v>
+        <v>2.9654</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7628</v>
+        <v>0.8698</v>
       </c>
       <c r="G13" t="n">
         <v>2.4285</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.1441</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7675</v>
+        <v>-0.4605</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2095</v>
+        <v>0.3164</v>
       </c>
       <c r="V13" t="n">
         <v>1.159</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3964</v>
+        <v>1.0803</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2047</v>
+        <v>-1.307</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6011</v>
+        <v>2.3873</v>
       </c>
       <c r="G14" t="n">
         <v>1.0096</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1127</v>
+        <v>-0.2035</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1735</v>
+        <v>-0.2758</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2862</v>
+        <v>0.0723</v>
       </c>
       <c r="V14" t="n">
         <v>0.6659</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. VIDAL PATIÑO</t>
+          <t>J. MARTINEZ FERREIRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0704</v>
+        <v>0.9169</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.8181</v>
+        <v>-1.9971</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7477</v>
+        <v>2.9141</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9976</v>
+        <v>-0.8794</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0483</v>
+        <v>-1.1207</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.046</v>
+        <v>0.2414</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.006</v>
+        <v>-1.4356</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3181</v>
+        <v>-1.2624</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3241</v>
+        <v>-0.1732</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0083</v>
+        <v>0.5562</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2698</v>
+        <v>0.1416</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2781</v>
+        <v>0.4145</v>
       </c>
       <c r="P15" t="n">
         <v>1.3709</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3709</v>
+        <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3861</v>
+        <v>0.4254</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7546</v>
+        <v>0.1423</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3685</v>
+        <v>0.283</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0576</v>
+        <v>0.2754</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ FERREIRO</t>
+          <t>F. VIDAL PATIÑO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1912</v>
+        <v>0.4726</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.9181</v>
+        <v>-1.4088</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7269</v>
+        <v>1.8814</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8794</v>
+        <v>-0.9976</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1207</v>
+        <v>0.0483</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2414</v>
+        <v>-1.046</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.4356</v>
+        <v>-1.006</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2624</v>
+        <v>0.3181</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1732</v>
+        <v>-1.3241</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5562</v>
+        <v>0.0083</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1416</v>
+        <v>-0.2698</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4145</v>
+        <v>0.2781</v>
       </c>
       <c r="P16" t="n">
         <v>1.3709</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3502</v>
+        <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6828</v>
+        <v>0.1569</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.3452</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0959</v>
+        <v>0.5021</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>-0.0576</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. AÑON DOSIL</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3294</v>
+        <v>-1.2737</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.8716</v>
+        <v>-3.7077</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5422</v>
+        <v>2.434</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.2929</v>
+        <v>-2.287</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.1661</v>
+        <v>0.9528</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1268</v>
+        <v>-3.2399</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.5616</v>
+        <v>-2.6484</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.965</v>
+        <v>0.0612</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5966</v>
+        <v>-2.7097</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7312</v>
+        <v>0.3614</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.201</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="O17" t="n">
         <v>-0.5302</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1958</v>
+        <v>1.9585</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7112000000000001</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6693</v>
+        <v>-1.0592</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0419</v>
+        <v>0.1141</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0564</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.0564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>A. AÑON DOSIL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6876</v>
+        <v>-1.547</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.0147</v>
+        <v>-3.3833</v>
       </c>
       <c r="F18" t="n">
-        <v>2.327</v>
+        <v>1.8362</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.287</v>
+        <v>-3.2929</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9528</v>
+        <v>-2.1661</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.2399</v>
+        <v>-1.1268</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.6484</v>
+        <v>-2.5616</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0612</v>
+        <v>-1.965</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.7097</v>
+        <v>-0.5966</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3614</v>
+        <v>-0.7312</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8915999999999999</v>
+        <v>-0.201</v>
       </c>
       <c r="O18" t="n">
         <v>-0.5302</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9585</v>
+        <v>0.1958</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3591</v>
+        <v>0.4936</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3662</v>
+        <v>0.1576</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0072</v>
+        <v>0.336</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.0564</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.0564</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1141</v>
+        <v>-1.6375</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.6641</v>
+        <v>-4.5617</v>
       </c>
       <c r="F19" t="n">
-        <v>2.55</v>
+        <v>2.9242</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3523</v>
@@ -1936,13 +1936,13 @@
         <v>2.7419</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2146</v>
+        <v>0.262</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0941</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2063</v>
+        <v>0.1679</v>
       </c>
       <c r="V19" t="n">
         <v>1.6071</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9143</v>
+        <v>-4.9678</v>
       </c>
       <c r="E20" t="n">
         <v>-5.4218</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5075</v>
+        <v>0.4541</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9403</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0743</v>
+        <v>-1.1278</v>
       </c>
       <c r="T20" t="n">
         <v>-0.8139999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2603</v>
+        <v>-0.3138</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3329</v>
@@ -2047,22 +2047,22 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>4.358</v>
+        <v>4.358099999999999</v>
       </c>
       <c r="E21" t="n">
         <v>-15.072</v>
       </c>
       <c r="F21" t="n">
-        <v>19.4299</v>
+        <v>19.4302</v>
       </c>
       <c r="G21" t="n">
         <v>-3.5668</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.749600000000001</v>
+        <v>-4.749599999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1827</v>
+        <v>1.182700000000001</v>
       </c>
       <c r="J21" t="n">
         <v>-2.3791</v>
@@ -2083,7 +2083,7 @@
         <v>-2.5992</v>
       </c>
       <c r="P21" t="n">
-        <v>2.937600000000001</v>
+        <v>2.9376</v>
       </c>
       <c r="Q21" t="n">
         <v>-14.6885</v>
@@ -2092,13 +2092,13 @@
         <v>17.6264</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9468000000000001</v>
+        <v>0.9469000000000005</v>
       </c>
       <c r="T21" t="n">
         <v>-2.032</v>
       </c>
       <c r="U21" t="n">
-        <v>2.979</v>
+        <v>2.9788</v>
       </c>
       <c r="V21" t="n">
         <v>4.0403</v>
@@ -2107,7 +2107,7 @@
         <v>4.0278</v>
       </c>
       <c r="X21" t="n">
-        <v>0.01250000000000018</v>
+        <v>0.01250000000000029</v>
       </c>
     </row>
   </sheetData>
